--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>profession</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>experience</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>preferred_domain_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>preferred_domain_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>preferred_domain_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>skills</t>
         </is>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,26 @@
           <t>skills</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>education_raw</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>work_experience_raw</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>projects_raw</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -517,6 +537,27 @@
           <t>Python, Java, SQL, AWS, Docker, Kubernetes, Git, REST APIs</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>University of Texas ; Austin, TX ; B.S. in Computer Science ; Aug 2015 - May 2019</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>TechCorp ; Austin, TX ; Senior Software Engineer ; Jan 2022 - Present ; Led migration of monolith to microservices on AWS EKS | Reduced API latency 40% by introducing Redis caching layer
+CodeWorks ; Remote ; Software Engineer ; Jun 2019 - Dec 2021 ; Built REST APIs serving 2M+ daily requests with Django and PostgreSQL</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Job Match AI ; Python, scikit-learn, Tkinter, n8n, Gemini ; 2026 ; Built a Random Forest job-matching engine with automated HR outreach | Reduced manual job application time by an estimated 80%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -567,6 +608,10 @@
           <t>Python, R, SQL, Statistics, Machine Learning, Pandas, NumPy</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -617,6 +662,10 @@
           <t>JavaScript, React, Node.js, HTML, CSS, MongoDB, Express</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,6 +716,10 @@
           <t>Python, TensorFlow, PyTorch, Deep Learning, Computer Vision, NLP</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,6 +770,10 @@
           <t>AWS, Azure, Docker, Kubernetes, Terraform, Jenkins, CI/CD, Python</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -767,6 +824,10 @@
           <t>Network Security, Python, Linux, Penetration Testing, Firewalls</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -817,6 +878,10 @@
           <t>Android, Kotlin, Java, Firebase, React Native, JavaScript</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -867,6 +932,10 @@
           <t>MySQL, PostgreSQL, SQL, Python, Database Design, Data Modeling</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,6 +986,10 @@
           <t>Docker, Kubernetes, Jenkins, Ansible, Terraform, AWS, Python, Bash</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -967,6 +1040,10 @@
           <t>Figma, Adobe XD, HTML, CSS, JavaScript, User Research, Wireframing</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1017,6 +1094,10 @@
           <t>Python, TensorFlow, PyTorch, Scikit-learn, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1065,6 +1146,151 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>JavaScript, React, Vue.js, HTML, CSS, Node.js, MongoDB</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>arjhungautam0246@gmail.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arjhun0246@</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recent Graduate</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Web Development</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>JavaScript, React, Vue.js, HTML, CSS, Node.js, MongoDB</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>University of Texas ; Austin, TX ; B.S. in Computer Science ; Aug 2015 - May 2019</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TechCorp ; Austin, TX ; Senior Software Engineer ; Jan 2022 - Present ; Led migration of monolith to microservices on AWS EKS | Reduced API latency 40% by introducing Redis caching layer
+CodeWorks ; Remote ; Software Engineer ; Jun 2019 - Dec 2021 ; Built REST APIs serving 2M+ daily requests with Django and PostgreSQL</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Job Match AI ; Python, scikit-learn, Tkinter, n8n, Gemini ; 2026 ; Built a Random Forest job-matching engine with automated HR outreach | Reduced manual job application time by an estimated 80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>arjhuncodes@gmail.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arjhun0246@</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Arjhun</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Web Development</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Full Stack developer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>React , Spring Boot , HTML , CSS , JavaScript</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Chennai , Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Government College of Engineering Bargur  ;Krishnagiri ;2023-2027</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DOTE ; Remote ;2024 - Present ;Developed and Maintained Transfer Application Poratal , Readmission , CFG and 7.5 Portal</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Transfer Application Portal ; Spring Boot , React , MySQL ; Application Saving , Dispaly and approval</t>
         </is>
       </c>
     </row>
